--- a/02_加值成品/八上/八上6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-2_三種難度測驗卷.xlsx
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>同族由上而下金屬性遞增</t>
+          <t>同族由上而下遞增：同一族元素由上往下排，原子半徑愈大、最外層電子愈容易失去，金屬性愈強，所以位置較下方的鉀比鈉的金屬性強</t>
         </is>
       </c>
     </row>
